--- a/ExperimentalResults/Result_tifs.xlsx
+++ b/ExperimentalResults/Result_tifs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data_backup\backup\科研资料\neckpass\neckpass提交github\NeckPass\ExperimentalResults\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{589FE477-6D53-44F4-A9E9-81FC94C16E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABE70F0-3EC0-437F-93EA-776493A21432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -370,12 +370,6 @@
     <t>8.3.7 Evaluation of Computational Delay</t>
   </si>
   <si>
-    <t>8.3.5 Impacts of Voting Mechanism</t>
-  </si>
-  <si>
-    <t>8.3.6. Impacts of Heart Rate Variations</t>
-  </si>
-  <si>
     <t>AUC</t>
   </si>
   <si>
@@ -392,6 +386,12 @@
   </si>
   <si>
     <t>4) Impacts of XR Devices</t>
+  </si>
+  <si>
+    <t>5) Impacts of Voting Mechanism</t>
+  </si>
+  <si>
+    <t>6) Physiological Stress Test</t>
   </si>
 </sst>
 </file>
@@ -1300,7 +1300,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C28" s="5">
         <v>0.98406099999999996</v>
@@ -1308,7 +1308,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C29" s="5">
         <v>4.1050000000000003E-2</v>
@@ -1358,7 +1358,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C2" s="7">
         <v>0</v>
@@ -1502,7 +1502,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>0</v>
@@ -1736,7 +1736,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>0</v>
@@ -1883,7 +1883,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>0</v>
@@ -2156,7 +2156,7 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>0</v>
@@ -2561,7 +2561,7 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>0</v>

--- a/ExperimentalResults/Result_tifs.xlsx
+++ b/ExperimentalResults/Result_tifs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data_backup\backup\科研资料\neckpass\neckpass提交github\NeckPass\ExperimentalResults\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABE70F0-3EC0-437F-93EA-776493A21432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99061025-1D45-49EA-ABB7-1F04AC4E21F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="8.2" sheetId="1" r:id="rId1"/>
@@ -73,9 +73,6 @@
     <t>TPR(3mo)</t>
   </si>
   <si>
-    <t>9.2 Impersonation Attack</t>
-  </si>
-  <si>
     <t>AED</t>
   </si>
   <si>
@@ -88,12 +85,6 @@
     <t>XM</t>
   </si>
   <si>
-    <t>9.3 Replay Attack</t>
-  </si>
-  <si>
-    <t>9.4 Spoofing Attack</t>
-  </si>
-  <si>
     <t>Chest_MQ2</t>
   </si>
   <si>
@@ -392,6 +383,15 @@
   </si>
   <si>
     <t>6) Physiological Stress Test</t>
+  </si>
+  <si>
+    <t>2) Impersonation Attack</t>
+  </si>
+  <si>
+    <t>3) Replay Attack</t>
+  </si>
+  <si>
+    <t>4) Spoofing Attack</t>
   </si>
 </sst>
 </file>
@@ -803,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>2</v>
@@ -823,7 +823,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>2</v>
@@ -843,7 +843,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>2</v>
@@ -863,7 +863,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>2</v>
@@ -883,7 +883,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>2</v>
@@ -903,7 +903,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>2</v>
@@ -923,7 +923,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>2</v>
@@ -943,7 +943,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>2</v>
@@ -963,7 +963,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>2</v>
@@ -983,7 +983,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>2</v>
@@ -1003,7 +1003,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>2</v>
@@ -1023,7 +1023,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>2</v>
@@ -1043,7 +1043,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>2</v>
@@ -1063,7 +1063,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>2</v>
@@ -1083,7 +1083,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>2</v>
@@ -1103,7 +1103,7 @@
         <v>15</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>2</v>
@@ -1123,7 +1123,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>2</v>
@@ -1143,7 +1143,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>2</v>
@@ -1163,7 +1163,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>2</v>
@@ -1183,7 +1183,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>2</v>
@@ -1203,7 +1203,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>2</v>
@@ -1223,7 +1223,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>2</v>
@@ -1243,7 +1243,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>2</v>
@@ -1263,7 +1263,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>2</v>
@@ -1300,7 +1300,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C28" s="5">
         <v>0.98406099999999996</v>
@@ -1308,7 +1308,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="7" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C29" s="5">
         <v>4.1050000000000003E-2</v>
@@ -1358,13 +1358,13 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C2" s="7">
         <v>0</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>2</v>
@@ -1382,7 +1382,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>2</v>
@@ -1400,7 +1400,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>2</v>
@@ -1418,7 +1418,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>2</v>
@@ -1436,7 +1436,7 @@
         <v>4</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>2</v>
@@ -1454,7 +1454,7 @@
         <v>5</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>2</v>
@@ -1472,7 +1472,7 @@
         <v>6</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>2</v>
@@ -1502,7 +1502,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>0</v>
@@ -1517,10 +1517,10 @@
         <v>9</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>2</v>
@@ -1529,10 +1529,10 @@
         <v>10</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>2</v>
@@ -1574,7 +1574,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>2</v>
@@ -1607,7 +1607,7 @@
         <v>2</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>2</v>
@@ -1640,7 +1640,7 @@
         <v>3</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>2</v>
@@ -1673,7 +1673,7 @@
         <v>4</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>2</v>
@@ -1736,7 +1736,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>0</v>
@@ -1763,7 +1763,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>2</v>
@@ -1784,7 +1784,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>2</v>
@@ -1805,7 +1805,7 @@
         <v>2</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>2</v>
@@ -1826,7 +1826,7 @@
         <v>3</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>2</v>
@@ -1847,7 +1847,7 @@
         <v>4</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>2</v>
@@ -1883,7 +1883,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>0</v>
@@ -1910,7 +1910,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>2</v>
@@ -1931,7 +1931,7 @@
         <v>1</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>2</v>
@@ -1952,7 +1952,7 @@
         <v>2</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>2</v>
@@ -1973,7 +1973,7 @@
         <v>3</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>2</v>
@@ -1994,7 +1994,7 @@
         <v>4</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>2</v>
@@ -2015,7 +2015,7 @@
         <v>5</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>2</v>
@@ -2036,7 +2036,7 @@
         <v>6</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>2</v>
@@ -2057,7 +2057,7 @@
         <v>7</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>2</v>
@@ -2078,7 +2078,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>2</v>
@@ -2099,7 +2099,7 @@
         <v>9</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>2</v>
@@ -2120,7 +2120,7 @@
         <v>10</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>2</v>
@@ -2156,7 +2156,7 @@
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>0</v>
@@ -2168,37 +2168,37 @@
         <v>2</v>
       </c>
       <c r="F41" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G41" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I41" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="G41" s="9" t="s">
+      <c r="J41" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="H41" s="9" t="s">
+      <c r="K41" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="L41" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="I41" s="9" t="s">
+      <c r="M41" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="J41" s="9" t="s">
+      <c r="N41" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="K41" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="L41" s="9" t="s">
+      <c r="O41" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="M41" s="9" t="s">
+      <c r="P41" s="9" t="s">
         <v>78</v>
-      </c>
-      <c r="N41" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="O41" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="P41" s="9" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.25">
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E42" s="9" t="s">
         <v>2</v>
@@ -2252,7 +2252,7 @@
         <v>1</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>2</v>
@@ -2297,7 +2297,7 @@
         <v>2</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E44" s="9" t="s">
         <v>2</v>
@@ -2342,7 +2342,7 @@
         <v>3</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>2</v>
@@ -2387,7 +2387,7 @@
         <v>4</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>2</v>
@@ -2432,7 +2432,7 @@
         <v>5</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>2</v>
@@ -2477,7 +2477,7 @@
         <v>6</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>2</v>
@@ -2561,7 +2561,7 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>0</v>
@@ -2573,25 +2573,25 @@
         <v>2</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I51" s="7" t="s">
         <v>2</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K51" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
@@ -2600,16 +2600,16 @@
         <v>0</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="H52" s="2">
         <v>0.64259999999999995</v>
@@ -2618,10 +2618,10 @@
         <v>2</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K52" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="L52" s="2">
         <v>0.93430000000000002</v>
@@ -2633,16 +2633,16 @@
         <v>1</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H53" s="2">
         <v>0.48320000000000002</v>
@@ -2651,10 +2651,10 @@
         <v>2</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="L53" s="2">
         <v>0.9556</v>
@@ -2666,16 +2666,16 @@
         <v>2</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="H54" s="2">
         <v>0.46679999999999999</v>
@@ -2684,10 +2684,10 @@
         <v>2</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="L54" s="2">
         <v>0.94910000000000005</v>
@@ -2703,10 +2703,10 @@
         <v>2</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H55" s="2">
         <v>0.53090000000000004</v>
@@ -2715,10 +2715,10 @@
         <v>2</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="L55" s="2">
         <v>0.94630000000000003</v>
@@ -2726,49 +2726,49 @@
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="12"/>
       <c r="C58" s="9" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="12"/>
       <c r="C59" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2801,7 +2801,7 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>11</v>
+        <v>115</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>0</v>
@@ -2828,7 +2828,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>2</v>
@@ -2849,7 +2849,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>2</v>
@@ -2870,7 +2870,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>2</v>
@@ -2891,7 +2891,7 @@
         <v>3</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>2</v>
@@ -2912,7 +2912,7 @@
         <v>4</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>2</v>
@@ -2933,7 +2933,7 @@
         <v>5</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>2</v>
@@ -2954,7 +2954,7 @@
         <v>6</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>2</v>
@@ -2975,7 +2975,7 @@
         <v>7</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>2</v>
@@ -3011,7 +3011,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>16</v>
+        <v>116</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>0</v>
@@ -3038,7 +3038,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>2</v>
@@ -3060,7 +3060,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>2</v>
@@ -3082,7 +3082,7 @@
         <v>2</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>2</v>
@@ -3104,7 +3104,7 @@
         <v>3</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>2</v>
@@ -3130,10 +3130,10 @@
         <v>2</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H17" s="2">
         <v>0.95350000000000001</v>
@@ -3141,7 +3141,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>17</v>
+        <v>117</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>0</v>
@@ -3168,7 +3168,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>2</v>
@@ -3189,7 +3189,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>2</v>
@@ -3210,7 +3210,7 @@
         <v>2</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>2</v>
@@ -3259,7 +3259,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>2</v>
@@ -3280,7 +3280,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>2</v>
@@ -3301,7 +3301,7 @@
         <v>2</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>2</v>

--- a/ExperimentalResults/Result_tifs.xlsx
+++ b/ExperimentalResults/Result_tifs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data_backup\backup\科研资料\neckpass\neckpass提交github\NeckPass\ExperimentalResults\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99061025-1D45-49EA-ABB7-1F04AC4E21F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{538EA43F-5383-46BF-8CFC-66F4BDC9C945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="118">
   <si>
     <t>No</t>
   </si>
@@ -3152,15 +3152,11 @@
       <c r="E19" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F19" s="7" t="s">
-        <v>3</v>
-      </c>
+      <c r="F19" s="7"/>
       <c r="G19" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H19" s="7" t="s">
-        <v>5</v>
-      </c>
+      <c r="H19" s="7"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
@@ -3173,15 +3169,11 @@
       <c r="E20" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F20" s="2">
-        <v>0.95379999999999998</v>
-      </c>
+      <c r="F20" s="2"/>
       <c r="G20" s="2">
         <v>0.95340000000000003</v>
       </c>
-      <c r="H20" s="2">
-        <v>0.9536</v>
-      </c>
+      <c r="H20" s="2"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
@@ -3194,15 +3186,11 @@
       <c r="E21" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F21" s="2">
-        <v>0.95069999999999999</v>
-      </c>
+      <c r="F21" s="2"/>
       <c r="G21" s="5">
         <v>0.94110000000000005</v>
       </c>
-      <c r="H21" s="2">
-        <v>0.94589999999999996</v>
-      </c>
+      <c r="H21" s="2"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
@@ -3215,15 +3203,11 @@
       <c r="E22" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F22" s="2">
-        <v>0.95069999999999999</v>
-      </c>
+      <c r="F22" s="2"/>
       <c r="G22" s="2">
         <v>0.94379999999999997</v>
       </c>
-      <c r="H22" s="2">
-        <v>0.94720000000000004</v>
-      </c>
+      <c r="H22" s="2"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
@@ -3243,15 +3227,11 @@
       <c r="E24" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F24" s="7" t="s">
-        <v>3</v>
-      </c>
+      <c r="F24" s="7"/>
       <c r="G24" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H24" s="7" t="s">
-        <v>5</v>
-      </c>
+      <c r="H24" s="7"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="13"/>
@@ -3264,15 +3244,11 @@
       <c r="E25" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F25" s="2">
-        <v>0.96599999999999997</v>
-      </c>
+      <c r="F25" s="2"/>
       <c r="G25" s="5">
         <v>0.90590000000000004</v>
       </c>
-      <c r="H25" s="2">
-        <v>0.93600000000000005</v>
-      </c>
+      <c r="H25" s="2"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
@@ -3285,15 +3261,11 @@
       <c r="E26" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F26" s="2">
-        <v>0.95930000000000004</v>
-      </c>
+      <c r="F26" s="2"/>
       <c r="G26" s="2">
         <v>1</v>
       </c>
-      <c r="H26" s="2">
-        <v>0.97970000000000002</v>
-      </c>
+      <c r="H26" s="2"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="13"/>
@@ -3306,15 +3278,11 @@
       <c r="E27" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F27" s="2">
-        <v>0.95930000000000004</v>
-      </c>
+      <c r="F27" s="2"/>
       <c r="G27" s="2">
         <v>0.98270000000000002</v>
       </c>
-      <c r="H27" s="2">
-        <v>0.97099999999999997</v>
-      </c>
+      <c r="H27" s="2"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G28" s="3">
